--- a/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_itra_2018_2019_including_DNFs_df.xlsx
+++ b/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_itra_2018_2019_including_DNFs_df.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16389" uniqueCount="2836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16391" uniqueCount="2836">
   <si>
     <t>Name</t>
   </si>
@@ -55075,6 +55075,9 @@
       <c r="B1353" t="s">
         <v>1676</v>
       </c>
+      <c r="C1353" t="s">
+        <v>1747</v>
+      </c>
       <c r="D1353">
         <v>40</v>
       </c>
@@ -61587,6 +61590,9 @@
       </c>
       <c r="B1545" t="s">
         <v>1676</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>1747</v>
       </c>
       <c r="D1545">
         <v>54</v>
